--- a/data/trans_orig/P5710-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P5710-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir consejos útiles cuando me ocurre algún acontecimiento importante en mi vida en 2007</t>
+          <t>Población según la frecuencia de recibir consejos útiles cuando me ocurre algún acontecimiento importante en mi vida en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>484226</t>
+          <t>478080</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>547683</t>
+          <t>544038</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>601008</t>
+          <t>602871</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>672383</t>
+          <t>676803</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1108343</t>
+          <t>1107003</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1200916</t>
+          <t>1198541</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,07%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>249064</t>
+          <t>250770</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>304191</t>
+          <t>306494</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>303935</t>
+          <t>300028</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>368647</t>
+          <t>363222</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>566344</t>
+          <t>567977</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>652472</t>
+          <t>652469</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>163504</t>
+          <t>162345</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>212478</t>
+          <t>210669</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>203156</t>
+          <t>205165</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>257534</t>
+          <t>258782</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>379214</t>
+          <t>379114</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>451609</t>
+          <t>453692</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,33%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34454</t>
+          <t>34770</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60733</t>
+          <t>61859</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77892</t>
+          <t>77931</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>115166</t>
+          <t>114119</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>119572</t>
+          <t>120753</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>164683</t>
+          <t>166767</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3003</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15237</t>
+          <t>14762</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8832</t>
+          <t>9358</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26053</t>
+          <t>25174</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14347</t>
+          <t>15201</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>34089</t>
+          <t>35009</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1053519</t>
+          <t>1055334</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1132010</t>
+          <t>1132310</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>902973</t>
+          <t>902622</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>980524</t>
+          <t>981643</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1976089</t>
+          <t>1976391</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2085798</t>
+          <t>2088153</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,64%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>382172</t>
+          <t>383409</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>453312</t>
+          <t>456259</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>384946</t>
+          <t>384359</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>454244</t>
+          <t>454208</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>787557</t>
+          <t>789157</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>886600</t>
+          <t>886995</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,03%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>128736</t>
+          <t>128025</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>177457</t>
+          <t>171437</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>155748</t>
+          <t>154149</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>207448</t>
+          <t>205071</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>294835</t>
+          <t>294820</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>364088</t>
+          <t>365842</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21760</t>
+          <t>22050</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46109</t>
+          <t>45036</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33125</t>
+          <t>32014</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60457</t>
+          <t>60532</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>59947</t>
+          <t>60624</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>94821</t>
+          <t>96864</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6174</t>
+          <t>6582</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>976</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8850</t>
+          <t>9034</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12405</t>
+          <t>12587</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>314907</t>
+          <t>312448</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>362224</t>
+          <t>361323</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>278754</t>
+          <t>277472</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>323641</t>
+          <t>321299</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>605925</t>
+          <t>605830</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>668838</t>
+          <t>671008</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>65,35%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>131519</t>
+          <t>130736</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>174297</t>
+          <t>176385</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>104439</t>
+          <t>106377</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>145143</t>
+          <t>144252</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>249333</t>
+          <t>244672</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>307045</t>
+          <t>304705</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,68%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>35345</t>
+          <t>36081</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>63522</t>
+          <t>64719</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28574</t>
+          <t>29213</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>53504</t>
+          <t>54026</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>70946</t>
+          <t>71199</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>107939</t>
+          <t>109965</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5334</t>
+          <t>5442</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19826</t>
+          <t>20257</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4769</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18052</t>
+          <t>17878</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11979</t>
+          <t>12183</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31260</t>
+          <t>31582</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5884</t>
+          <t>5386</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7639</t>
+          <t>7597</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8450</t>
+          <t>8757</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1886294</t>
+          <t>1888168</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1997171</t>
+          <t>2002761</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1818350</t>
+          <t>1822965</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1941078</t>
+          <t>1938194</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3743118</t>
+          <t>3749121</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3910400</t>
+          <t>3905908</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>58,69%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>801419</t>
+          <t>794750</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>903240</t>
+          <t>897216</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>827125</t>
+          <t>824157</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>939668</t>
+          <t>932696</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1654045</t>
+          <t>1652903</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1798798</t>
+          <t>1795860</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,99%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>346828</t>
+          <t>345182</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>422984</t>
+          <t>422155</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>411818</t>
+          <t>410181</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>493697</t>
+          <t>491404</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>778533</t>
+          <t>778975</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>887055</t>
+          <t>883565</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,28%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>71732</t>
+          <t>70467</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>111882</t>
+          <t>111053</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>126572</t>
+          <t>126477</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>173427</t>
+          <t>177074</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>205874</t>
+          <t>208490</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>270007</t>
+          <t>271605</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5087</t>
+          <t>5770</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18615</t>
+          <t>18909</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>13055</t>
+          <t>12494</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>32979</t>
+          <t>32318</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>20927</t>
+          <t>20342</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>44058</t>
+          <t>43745</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir consejos útiles cuando me ocurre algún acontecimiento importante en mi vida en 2012</t>
+          <t>Población según la frecuencia de recibir consejos útiles cuando me ocurre algún acontecimiento importante en mi vida en 2012 (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>496361</t>
+          <t>500924</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>559118</t>
+          <t>568224</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>646432</t>
+          <t>645646</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>721914</t>
+          <t>724676</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1170639</t>
+          <t>1168785</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1266468</t>
+          <t>1267982</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>55,1%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>234171</t>
+          <t>231485</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>289543</t>
+          <t>286484</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>396754</t>
+          <t>399060</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>469210</t>
+          <t>472852</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>649345</t>
+          <t>648272</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>739436</t>
+          <t>741633</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>114365</t>
+          <t>114695</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>159897</t>
+          <t>159579</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>134833</t>
+          <t>134451</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>182706</t>
+          <t>182442</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>260848</t>
+          <t>261496</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>327488</t>
+          <t>326448</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24333</t>
+          <t>24215</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49095</t>
+          <t>48830</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22584</t>
+          <t>22069</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44508</t>
+          <t>43822</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50890</t>
+          <t>51714</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83383</t>
+          <t>84300</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>3988</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15094</t>
+          <t>15465</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13539</t>
+          <t>13120</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33323</t>
+          <t>34183</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>19917</t>
+          <t>20221</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>43252</t>
+          <t>42652</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1160313</t>
+          <t>1156748</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1245802</t>
+          <t>1248632</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>980756</t>
+          <t>985231</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1069168</t>
+          <t>1067024</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2171280</t>
+          <t>2163550</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2290120</t>
+          <t>2290211</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>510203</t>
+          <t>509382</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>590616</t>
+          <t>595211</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>456639</t>
+          <t>461917</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>537888</t>
+          <t>536462</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>992682</t>
+          <t>994267</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1101462</t>
+          <t>1108580</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,81%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>140693</t>
+          <t>137849</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>189778</t>
+          <t>191931</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>151635</t>
+          <t>154656</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>205897</t>
+          <t>206249</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>307345</t>
+          <t>307965</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>376347</t>
+          <t>378938</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26427</t>
+          <t>26738</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53562</t>
+          <t>53434</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31055</t>
+          <t>30762</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59190</t>
+          <t>58415</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,47 +4763,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>3,33%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>81929</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>65882</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>102618</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>1,77%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>81929</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>66286</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>104577</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3039</t>
+          <t>2936</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14728</t>
+          <t>13606</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5879</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21440</t>
+          <t>21613</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10952</t>
+          <t>10964</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>29846</t>
+          <t>30631</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>289277</t>
+          <t>290738</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>335354</t>
+          <t>332892</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>296306</t>
+          <t>295433</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>338412</t>
+          <t>338058</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>599901</t>
+          <t>599823</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>657547</t>
+          <t>662600</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>70,81%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>102390</t>
+          <t>103704</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>143746</t>
+          <t>144600</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>85377</t>
+          <t>85077</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>124933</t>
+          <t>125959</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>198717</t>
+          <t>196947</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>252610</t>
+          <t>255786</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,33%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26458</t>
+          <t>26299</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>52964</t>
+          <t>50874</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20168</t>
+          <t>20834</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44941</t>
+          <t>45559</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>52561</t>
+          <t>51272</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>88066</t>
+          <t>89193</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12086</t>
+          <t>11259</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6674</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>2962</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14160</t>
+          <t>14514</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4503</t>
+          <t>4516</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7271</t>
+          <t>6745</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>895</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9417</t>
+          <t>8507</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1982689</t>
+          <t>1988613</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2099688</t>
+          <t>2102197</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1970404</t>
+          <t>1971657</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2089622</t>
+          <t>2094769</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3996316</t>
+          <t>4002374</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4158482</t>
+          <t>4169321</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>59,94%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>885506</t>
+          <t>880385</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>990808</t>
+          <t>986066</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>981753</t>
+          <t>976864</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1091135</t>
+          <t>1087325</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1882493</t>
+          <t>1876755</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2043797</t>
+          <t>2031572</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,21%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>304776</t>
+          <t>304743</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>374535</t>
+          <t>373950</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>332647</t>
+          <t>330942</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>405004</t>
+          <t>404035</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>649349</t>
+          <t>657049</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>758090</t>
+          <t>758866</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,91%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>61045</t>
+          <t>60695</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>99156</t>
+          <t>98906</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>61662</t>
+          <t>61049</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>98699</t>
+          <t>96783</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>131784</t>
+          <t>130551</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>181046</t>
+          <t>182023</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9398</t>
+          <t>9689</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24723</t>
+          <t>25352</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>24756</t>
+          <t>24029</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>49783</t>
+          <t>49115</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>37678</t>
+          <t>37815</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>68542</t>
+          <t>68309</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir consejos útiles cuando me ocurre algún acontecimiento importante en mi vida en 2016</t>
+          <t>Población según la frecuencia de recibir consejos útiles cuando me ocurre algún acontecimiento importante en mi vida en 2016 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>310356</t>
+          <t>309893</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>364003</t>
+          <t>363379</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>397184</t>
+          <t>397497</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>463952</t>
+          <t>463019</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>724197</t>
+          <t>725285</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>810061</t>
+          <t>806120</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,12%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>240513</t>
+          <t>241591</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>291494</t>
+          <t>293232</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>325358</t>
+          <t>326176</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>387964</t>
+          <t>389543</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>586765</t>
+          <t>584804</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>667175</t>
+          <t>667067</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>95020</t>
+          <t>95213</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>131984</t>
+          <t>135393</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136023</t>
+          <t>137493</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>186942</t>
+          <t>187326</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>243235</t>
+          <t>243051</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>307999</t>
+          <t>307070</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,57%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23742</t>
+          <t>23287</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45076</t>
+          <t>44530</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20257</t>
+          <t>22060</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44813</t>
+          <t>46281</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50960</t>
+          <t>49293</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81813</t>
+          <t>80624</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10415</t>
+          <t>10138</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>20695</t>
+          <t>20666</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8535</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25878</t>
+          <t>24308</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>954963</t>
+          <t>955634</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1052736</t>
+          <t>1048808</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>958855</t>
+          <t>962090</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1049938</t>
+          <t>1052645</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1946825</t>
+          <t>1950846</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2072037</t>
+          <t>2073285</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>51,11%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>694015</t>
+          <t>693699</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>787028</t>
+          <t>779528</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>655399</t>
+          <t>656872</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>744119</t>
+          <t>745202</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1380438</t>
+          <t>1374713</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1496629</t>
+          <t>1496469</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>238548</t>
+          <t>242706</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>300551</t>
+          <t>304742</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>210461</t>
+          <t>207630</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>270559</t>
+          <t>268540</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>465247</t>
+          <t>464726</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>548247</t>
+          <t>553860</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,65%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34861</t>
+          <t>35129</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63417</t>
+          <t>63679</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22027</t>
+          <t>21907</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45423</t>
+          <t>44395</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60440</t>
+          <t>62148</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>98826</t>
+          <t>98654</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6934</t>
+          <t>7338</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22613</t>
+          <t>21787</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6269</t>
+          <t>5414</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20525</t>
+          <t>19397</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15679</t>
+          <t>16425</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36628</t>
+          <t>37351</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>281082</t>
+          <t>279851</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>330013</t>
+          <t>329003</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>297949</t>
+          <t>299689</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>347759</t>
+          <t>348578</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>596826</t>
+          <t>599819</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>662240</t>
+          <t>663488</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,64%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>165569</t>
+          <t>168052</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>212483</t>
+          <t>217423</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>148183</t>
+          <t>147689</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>192933</t>
+          <t>193994</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>324756</t>
+          <t>324675</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>388794</t>
+          <t>388117</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,47%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>38853</t>
+          <t>36250</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>64771</t>
+          <t>65894</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32131</t>
+          <t>31197</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>58663</t>
+          <t>57421</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>77045</t>
+          <t>75291</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>115629</t>
+          <t>114553</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -8359,7 +8359,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>4565</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18349</t>
+          <t>18214</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5408</t>
+          <t>4713</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19222</t>
+          <t>18526</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -8467,97 +8467,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2092</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1584510</t>
+          <t>1588482</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1702941</t>
+          <t>1708416</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1700344</t>
+          <t>1698128</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1821779</t>
+          <t>1821239</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3316980</t>
+          <t>3320078</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3491840</t>
+          <t>3492593</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,63%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1141000</t>
+          <t>1139927</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1255439</t>
+          <t>1250105</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1167996</t>
+          <t>1162927</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1284481</t>
+          <t>1286332</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2344822</t>
+          <t>2341183</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2503283</t>
+          <t>2505208</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,31%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>396930</t>
+          <t>396864</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>476115</t>
+          <t>474854</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>400601</t>
+          <t>406653</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>480420</t>
+          <t>487034</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>821107</t>
+          <t>821421</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>935519</t>
+          <t>931014</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,5%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>64069</t>
+          <t>64900</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>99139</t>
+          <t>101263</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,82 +9051,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>72569</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>55584</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>92027</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>153440</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>130886</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>183209</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>1,9%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,94%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>72569</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>57134</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>95708</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>2,71%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>153440</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>129130</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>180319</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9834</t>
+          <t>9898</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>27411</t>
+          <t>27646</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14481</t>
+          <t>14261</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>35132</t>
+          <t>34602</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>29112</t>
+          <t>28807</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>55148</t>
+          <t>54841</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir consejos útiles cuando me ocurre algún acontecimiento importante en mi vida en 2023</t>
+          <t>Población según la frecuencia de recibir consejos útiles cuando me ocurre algún acontecimiento importante en mi vida en 2023 (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9610,12 +9610,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>215756</t>
+          <t>215305</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>256568</t>
+          <t>255591</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9625,12 +9625,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>305330</t>
+          <t>305011</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>349012</t>
+          <t>348265</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9680,12 +9680,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>531238</t>
+          <t>532804</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>592613</t>
+          <t>594862</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9695,12 +9695,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>47,27%</t>
         </is>
       </c>
     </row>
@@ -9723,12 +9723,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>131653</t>
+          <t>131901</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>168755</t>
+          <t>169222</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>208904</t>
+          <t>209848</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>247562</t>
+          <t>247587</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>350745</t>
+          <t>352553</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>405896</t>
+          <t>404750</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,16%</t>
         </is>
       </c>
     </row>
@@ -9836,12 +9836,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>59619</t>
+          <t>57905</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>88468</t>
+          <t>88168</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9851,12 +9851,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>107115</t>
+          <t>106604</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136727</t>
+          <t>137405</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9886,12 +9886,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>176072</t>
+          <t>175753</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>215203</t>
+          <t>216242</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,18%</t>
         </is>
       </c>
     </row>
@@ -9949,12 +9949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31812</t>
+          <t>31073</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52510</t>
+          <t>52284</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9984,12 +9984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42303</t>
+          <t>42999</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63099</t>
+          <t>62295</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>78035</t>
+          <t>79338</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>108349</t>
+          <t>108470</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6948</t>
+          <t>7222</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19434</t>
+          <t>19620</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12979</t>
+          <t>12811</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25823</t>
+          <t>25309</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>23429</t>
+          <t>22179</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>41815</t>
+          <t>40748</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -10292,12 +10292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1217146</t>
+          <t>1217096</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1632443</t>
+          <t>1669356</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>756081</t>
+          <t>816581</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1281059</t>
+          <t>1283286</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10342,12 +10342,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2181491</t>
+          <t>2207428</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2773896</t>
+          <t>2813127</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>62,21%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>502348</t>
+          <t>463286</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>807819</t>
+          <t>803906</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>460212</t>
+          <t>478416</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>749509</t>
+          <t>744725</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1094185</t>
+          <t>1061264</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1524527</t>
+          <t>1505451</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,29%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>119449</t>
+          <t>118859</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>209738</t>
+          <t>212320</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>113456</t>
+          <t>115417</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>187574</t>
+          <t>187045</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>266464</t>
+          <t>263446</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>383691</t>
+          <t>380564</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31219</t>
+          <t>31016</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62525</t>
+          <t>62634</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,7 +10646,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60209</t>
+          <t>59131</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>900731</t>
+          <t>794574</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>106524</t>
+          <t>104674</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1148932</t>
+          <t>931266</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>20,6%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8519</t>
+          <t>9269</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25324</t>
+          <t>24676</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>9464</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30835</t>
+          <t>28623</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>21514</t>
+          <t>22569</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46422</t>
+          <t>47546</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>361988</t>
+          <t>359681</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>417940</t>
+          <t>417355</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>428856</t>
+          <t>426946</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>469064</t>
+          <t>467841</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>803131</t>
+          <t>806185</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>870191</t>
+          <t>872809</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>67,0%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>166485</t>
+          <t>166203</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>213845</t>
+          <t>218117</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>147582</t>
+          <t>148646</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>185590</t>
+          <t>183106</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>329091</t>
+          <t>328628</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>389361</t>
+          <t>385734</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,61%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25144</t>
+          <t>24705</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49531</t>
+          <t>49400</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24238</t>
+          <t>24324</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44870</t>
+          <t>45584</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>54382</t>
+          <t>54373</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>85720</t>
+          <t>85166</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9210</t>
+          <t>9131</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27343</t>
+          <t>30292</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4170</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13413</t>
+          <t>13415</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15825</t>
+          <t>15515</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37758</t>
+          <t>36221</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -11426,12 +11426,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1469</t>
+          <t>1509</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47838</t>
+          <t>52658</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11446,7 +11446,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>662</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6360</t>
+          <t>6912</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11481,7 +11481,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3968</t>
+          <t>3779</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>47228</t>
+          <t>52541</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1838267</t>
+          <t>1836656</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2275043</t>
+          <t>2291690</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1583002</t>
+          <t>1534584</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2062992</t>
+          <t>2058275</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3589344</t>
+          <t>3569820</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4241859</t>
+          <t>4202429</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>59,33%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>830008</t>
+          <t>819248</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1147344</t>
+          <t>1143854</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>873589</t>
+          <t>852099</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1133606</t>
+          <t>1134702</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1814584</t>
+          <t>1824848</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2237267</t>
+          <t>2241758</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,65%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>221796</t>
+          <t>220472</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>322988</t>
+          <t>325757</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>257414</t>
+          <t>249322</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>349310</t>
+          <t>346208</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>516160</t>
+          <t>518245</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>653434</t>
+          <t>656576</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>80876</t>
+          <t>79222</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>126508</t>
+          <t>128038</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>119209</t>
+          <t>119823</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>838032</t>
+          <t>952505</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>218732</t>
+          <t>220607</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1121810</t>
+          <t>1127019</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,91%</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>24966</t>
+          <t>24934</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>74482</t>
+          <t>77336</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12128,7 +12128,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>27899</t>
+          <t>27332</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>51395</t>
+          <t>51187</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12158,7 +12158,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>58418</t>
+          <t>59418</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>111390</t>
+          <t>109949</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P5710-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P5710-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>478080</t>
+          <t>481705</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>544038</t>
+          <t>544853</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>602871</t>
+          <t>603880</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>676803</t>
+          <t>673117</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1107003</t>
+          <t>1103658</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1198541</t>
+          <t>1204170</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>51,31%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>250770</t>
+          <t>248102</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>306494</t>
+          <t>304342</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>300028</t>
+          <t>307030</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>363222</t>
+          <t>365682</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>567977</t>
+          <t>570354</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>652469</t>
+          <t>653275</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,84%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>162345</t>
+          <t>163294</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>210669</t>
+          <t>214877</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>205165</t>
+          <t>205067</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>258782</t>
+          <t>258994</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>379114</t>
+          <t>380130</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>453692</t>
+          <t>453466</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,32%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34770</t>
+          <t>34478</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61859</t>
+          <t>61340</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77931</t>
+          <t>77745</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>114119</t>
+          <t>114576</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>120753</t>
+          <t>119767</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>166767</t>
+          <t>165388</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2836</t>
+          <t>3068</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14762</t>
+          <t>15165</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9358</t>
+          <t>9168</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25174</t>
+          <t>25587</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15201</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>35009</t>
+          <t>35025</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1055334</t>
+          <t>1054471</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1132310</t>
+          <t>1131827</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>902622</t>
+          <t>902875</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>981643</t>
+          <t>979888</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1976391</t>
+          <t>1972121</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2088153</t>
+          <t>2090406</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>63,71%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>383409</t>
+          <t>384211</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>456259</t>
+          <t>453877</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>384359</t>
+          <t>385854</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>454208</t>
+          <t>454331</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>789157</t>
+          <t>793268</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>886995</t>
+          <t>892827</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,21%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>128025</t>
+          <t>126703</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>171437</t>
+          <t>173433</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>154149</t>
+          <t>155928</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>205071</t>
+          <t>205385</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>294820</t>
+          <t>295139</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>365842</t>
+          <t>364565</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,11%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22050</t>
+          <t>22645</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45036</t>
+          <t>46325</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32014</t>
+          <t>32154</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60532</t>
+          <t>59576</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60624</t>
+          <t>60543</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96864</t>
+          <t>97266</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6582</t>
+          <t>6166</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>974</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9034</t>
+          <t>9617</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>1987</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12587</t>
+          <t>11812</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>312448</t>
+          <t>313980</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>361323</t>
+          <t>361819</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>277472</t>
+          <t>280483</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>321299</t>
+          <t>321371</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>605830</t>
+          <t>606998</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>671008</t>
+          <t>671411</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>65,39%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>130736</t>
+          <t>129850</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>176385</t>
+          <t>176792</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>106377</t>
+          <t>104737</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>144252</t>
+          <t>143508</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>244672</t>
+          <t>247968</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>304705</t>
+          <t>305509</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,76%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36081</t>
+          <t>35167</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>64719</t>
+          <t>63448</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>29213</t>
+          <t>29533</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>54026</t>
+          <t>56534</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>71199</t>
+          <t>72010</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>109965</t>
+          <t>110036</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5442</t>
+          <t>5075</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20257</t>
+          <t>18764</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4703</t>
+          <t>4397</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17878</t>
+          <t>18667</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12183</t>
+          <t>12616</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31582</t>
+          <t>33045</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5386</t>
+          <t>5290</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7597</t>
+          <t>7251</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8757</t>
+          <t>8881</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1888168</t>
+          <t>1888238</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2002761</t>
+          <t>1998390</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1822965</t>
+          <t>1825180</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1938194</t>
+          <t>1937639</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3749121</t>
+          <t>3749145</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3905908</t>
+          <t>3911954</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,79%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>794750</t>
+          <t>799872</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>897216</t>
+          <t>900640</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>824157</t>
+          <t>829624</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>932696</t>
+          <t>929376</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1652903</t>
+          <t>1655632</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1795860</t>
+          <t>1798595</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,03%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>345182</t>
+          <t>347865</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>422155</t>
+          <t>421066</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>410181</t>
+          <t>409744</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>491404</t>
+          <t>484985</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>778975</t>
+          <t>781107</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>883565</t>
+          <t>890008</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>70467</t>
+          <t>72919</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>111053</t>
+          <t>110509</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>126477</t>
+          <t>126463</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>177074</t>
+          <t>175528</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>208490</t>
+          <t>211583</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>271605</t>
+          <t>271942</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5770</t>
+          <t>5077</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18909</t>
+          <t>19262</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12494</t>
+          <t>11727</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>32318</t>
+          <t>30525</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>20342</t>
+          <t>20428</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>43745</t>
+          <t>44086</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>500924</t>
+          <t>494406</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>568224</t>
+          <t>561951</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>645646</t>
+          <t>649238</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>724676</t>
+          <t>724569</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1168785</t>
+          <t>1167373</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1267982</t>
+          <t>1264593</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>54,95%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>231485</t>
+          <t>232286</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>286484</t>
+          <t>289641</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>399060</t>
+          <t>397992</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>472852</t>
+          <t>465016</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>648272</t>
+          <t>647294</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>741633</t>
+          <t>738334</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,08%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>114695</t>
+          <t>116106</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>159579</t>
+          <t>161519</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>134451</t>
+          <t>133666</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>182442</t>
+          <t>184418</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>261496</t>
+          <t>264706</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>326448</t>
+          <t>326871</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24215</t>
+          <t>23279</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48830</t>
+          <t>47844</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22069</t>
+          <t>21835</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43822</t>
+          <t>44706</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51714</t>
+          <t>52386</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84300</t>
+          <t>85208</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3988</t>
+          <t>3762</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15465</t>
+          <t>14682</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13120</t>
+          <t>13959</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>34183</t>
+          <t>33308</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20221</t>
+          <t>20164</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>42652</t>
+          <t>42115</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1156748</t>
+          <t>1151697</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1248632</t>
+          <t>1246235</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>985231</t>
+          <t>986770</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1067024</t>
+          <t>1069251</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2163550</t>
+          <t>2161660</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2290211</t>
+          <t>2285843</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>61,47%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>509382</t>
+          <t>509124</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>595211</t>
+          <t>596152</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>461917</t>
+          <t>458649</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>536462</t>
+          <t>536822</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>994267</t>
+          <t>995622</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1108580</t>
+          <t>1106705</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,76%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>137849</t>
+          <t>142038</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>191931</t>
+          <t>189681</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>154656</t>
+          <t>152986</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>206249</t>
+          <t>207407</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>307965</t>
+          <t>305369</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>378938</t>
+          <t>378741</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26738</t>
+          <t>27832</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53434</t>
+          <t>55143</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30762</t>
+          <t>31082</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58415</t>
+          <t>58763</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65882</t>
+          <t>65725</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>102618</t>
+          <t>104013</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2936</t>
+          <t>2950</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13606</t>
+          <t>13248</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5942</t>
+          <t>5909</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21613</t>
+          <t>21274</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10964</t>
+          <t>11838</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>30631</t>
+          <t>31826</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>290738</t>
+          <t>289415</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>332892</t>
+          <t>334751</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>295433</t>
+          <t>296018</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>338058</t>
+          <t>337400</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>599823</t>
+          <t>599421</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>662600</t>
+          <t>657815</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,3%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>103704</t>
+          <t>103715</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>144600</t>
+          <t>145712</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>85077</t>
+          <t>87779</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>125959</t>
+          <t>125654</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>196947</t>
+          <t>199540</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>255786</t>
+          <t>255128</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,26%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26299</t>
+          <t>26703</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50874</t>
+          <t>52259</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20834</t>
+          <t>20431</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45559</t>
+          <t>45992</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>51272</t>
+          <t>54231</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>89193</t>
+          <t>90886</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11259</t>
+          <t>11843</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,39 +5410,39 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1909</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6379</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
           <t>0,42%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,35%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>1909</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2962</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14514</t>
+          <t>14312</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4516</t>
+          <t>4567</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6745</t>
+          <t>7795</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>887</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8507</t>
+          <t>8576</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1988613</t>
+          <t>1986092</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2102197</t>
+          <t>2105581</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1971657</t>
+          <t>1970785</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2094769</t>
+          <t>2091846</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4002374</t>
+          <t>3993170</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4169321</t>
+          <t>4161200</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>59,83%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>880385</t>
+          <t>879751</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>986066</t>
+          <t>987663</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>976864</t>
+          <t>978034</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1087325</t>
+          <t>1088962</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1876755</t>
+          <t>1889094</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2031572</t>
+          <t>2048489</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,45%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>304743</t>
+          <t>304646</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>373950</t>
+          <t>371944</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>330942</t>
+          <t>332368</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>404035</t>
+          <t>407058</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>657049</t>
+          <t>645782</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>758866</t>
+          <t>756970</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>60695</t>
+          <t>61846</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>98906</t>
+          <t>99936</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>61049</t>
+          <t>60128</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>96783</t>
+          <t>97712</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>130551</t>
+          <t>129931</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>182023</t>
+          <t>182304</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9689</t>
+          <t>9632</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25352</t>
+          <t>25559</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6210,72 +6210,72 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>35458</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>24834</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>49827</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>51423</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>38058</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>68041</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
           <t>0,74%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>35458</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>24029</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>49115</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>51423</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>37815</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>68309</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>309893</t>
+          <t>310114</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>363379</t>
+          <t>364878</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>397497</t>
+          <t>396953</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>463019</t>
+          <t>462605</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>725285</t>
+          <t>723355</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>806120</t>
+          <t>806640</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>46,15%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>241591</t>
+          <t>242094</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>293232</t>
+          <t>293638</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>326176</t>
+          <t>326743</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>389543</t>
+          <t>388363</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>584804</t>
+          <t>583822</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>667067</t>
+          <t>664419</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,02%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>95213</t>
+          <t>95608</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>135393</t>
+          <t>133967</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>137493</t>
+          <t>138811</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>187326</t>
+          <t>187551</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>243051</t>
+          <t>245410</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>307070</t>
+          <t>309123</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,69%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23287</t>
+          <t>23053</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44530</t>
+          <t>46176</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22060</t>
+          <t>20855</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46281</t>
+          <t>44571</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49293</t>
+          <t>49379</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>80624</t>
+          <t>80385</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>966</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10138</t>
+          <t>9763</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>20666</t>
+          <t>21521</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>7818</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24308</t>
+          <t>24657</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>955634</t>
+          <t>955076</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1048808</t>
+          <t>1049586</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>962090</t>
+          <t>963677</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1052645</t>
+          <t>1050514</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1950846</t>
+          <t>1951311</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2073285</t>
+          <t>2074022</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>51,13%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>693699</t>
+          <t>697671</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>779528</t>
+          <t>783832</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>656872</t>
+          <t>658188</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>745202</t>
+          <t>739829</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1374713</t>
+          <t>1374545</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1496469</t>
+          <t>1498299</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,93%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>242706</t>
+          <t>241797</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>304742</t>
+          <t>304801</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>207630</t>
+          <t>209304</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>268540</t>
+          <t>269666</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>464726</t>
+          <t>466829</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>553860</t>
+          <t>555257</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,69%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35129</t>
+          <t>33705</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63679</t>
+          <t>62605</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21907</t>
+          <t>20153</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44395</t>
+          <t>43846</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>62148</t>
+          <t>60903</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>98654</t>
+          <t>97930</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7338</t>
+          <t>6569</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21787</t>
+          <t>21601</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5414</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19397</t>
+          <t>19163</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16425</t>
+          <t>16097</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37351</t>
+          <t>36551</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>279851</t>
+          <t>280677</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>329003</t>
+          <t>329076</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>299689</t>
+          <t>301265</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>348578</t>
+          <t>346482</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>599819</t>
+          <t>595206</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>663488</t>
+          <t>661565</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>60,46%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>168052</t>
+          <t>164537</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>217423</t>
+          <t>210551</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>147689</t>
+          <t>149111</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>193994</t>
+          <t>191651</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>324675</t>
+          <t>327718</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>388117</t>
+          <t>390838</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,72%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36250</t>
+          <t>37701</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>65894</t>
+          <t>68452</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31197</t>
+          <t>33019</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>57421</t>
+          <t>59860</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>75291</t>
+          <t>76486</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>114553</t>
+          <t>115889</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -8359,7 +8359,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>4416</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18214</t>
+          <t>18249</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4713</t>
+          <t>5135</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18526</t>
+          <t>18652</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1588482</t>
+          <t>1584041</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1708416</t>
+          <t>1704555</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1698128</t>
+          <t>1698462</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1821239</t>
+          <t>1822250</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3320078</t>
+          <t>3319897</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3492593</t>
+          <t>3490209</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,59%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1139927</t>
+          <t>1142029</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1250105</t>
+          <t>1252311</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1162927</t>
+          <t>1168995</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1286332</t>
+          <t>1281421</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2341183</t>
+          <t>2333607</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2505208</t>
+          <t>2503392</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,29%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>396864</t>
+          <t>395929</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>474854</t>
+          <t>474655</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>406653</t>
+          <t>405873</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>487034</t>
+          <t>488552</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>821421</t>
+          <t>822253</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>931014</t>
+          <t>937131</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>64900</t>
+          <t>65425</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>101263</t>
+          <t>102018</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>55584</t>
+          <t>56784</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>92027</t>
+          <t>92813</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>130886</t>
+          <t>128357</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>183209</t>
+          <t>181048</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9898</t>
+          <t>10109</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>27646</t>
+          <t>27826</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14261</t>
+          <t>14931</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>34602</t>
+          <t>35109</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>28807</t>
+          <t>28939</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>54841</t>
+          <t>56223</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -9605,32 +9605,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>235353</t>
+          <t>262834</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>215305</t>
+          <t>241367</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>255591</t>
+          <t>287160</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9640,32 +9640,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>326294</t>
+          <t>345500</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>305011</t>
+          <t>324046</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>348265</t>
+          <t>369062</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9675,32 +9675,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>561647</t>
+          <t>608334</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>532804</t>
+          <t>575209</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>594862</t>
+          <t>641168</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>46,2%</t>
         </is>
       </c>
     </row>
@@ -9718,32 +9718,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>150155</t>
+          <t>164980</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>131901</t>
+          <t>145442</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>169222</t>
+          <t>186626</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9753,67 +9753,67 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>228650</t>
+          <t>254765</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>209848</t>
+          <t>235004</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>247587</t>
+          <t>277187</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
+          <t>28,91%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>34,1%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>419745</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>389942</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>448810</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>30,24%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>28,1%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>33,15%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>635</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>378805</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>352553</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>404750</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>30,1%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>28,02%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,34%</t>
         </is>
       </c>
     </row>
@@ -9831,32 +9831,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>73144</t>
+          <t>87879</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57905</t>
+          <t>70918</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>88168</t>
+          <t>106442</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9866,67 +9866,67 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>121191</t>
+          <t>132885</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>106604</t>
+          <t>117749</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>137405</t>
+          <t>150363</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
+          <t>14,49%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>18,5%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>220764</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>198006</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>244043</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>15,91%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
           <t>14,27%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>18,4%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>194335</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>175753</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>216242</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>15,44%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>13,97%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -9944,32 +9944,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40663</t>
+          <t>46454</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31073</t>
+          <t>35893</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52284</t>
+          <t>61217</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9979,32 +9979,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>52111</t>
+          <t>57966</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42999</t>
+          <t>46994</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62295</t>
+          <t>69843</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10014,32 +10014,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>92774</t>
+          <t>104421</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>79338</t>
+          <t>88279</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>108470</t>
+          <t>121197</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>12184</t>
+          <t>12860</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7222</t>
+          <t>7555</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19620</t>
+          <t>20543</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10092,32 +10092,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>18662</t>
+          <t>21742</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12811</t>
+          <t>15029</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25309</t>
+          <t>29778</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10127,32 +10127,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>30847</t>
+          <t>34602</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22179</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>40748</t>
+          <t>45566</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -10170,17 +10170,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>511500</t>
+          <t>575008</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>511500</t>
+          <t>575008</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>511500</t>
+          <t>575008</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10205,17 +10205,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>746909</t>
+          <t>812858</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>746909</t>
+          <t>812858</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>746909</t>
+          <t>812858</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10240,17 +10240,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1258409</t>
+          <t>1387866</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1258409</t>
+          <t>1387866</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1258409</t>
+          <t>1387866</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10287,32 +10287,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1348073</t>
+          <t>1176000</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1217096</t>
+          <t>1123455</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1669356</t>
+          <t>1232106</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10322,32 +10322,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1139604</t>
+          <t>1154121</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>816581</t>
+          <t>1111909</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1283286</t>
+          <t>1199826</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10357,32 +10357,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2487676</t>
+          <t>2330121</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2207428</t>
+          <t>2251569</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2813127</t>
+          <t>2395530</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>54,51%</t>
         </is>
       </c>
     </row>
@@ -10400,32 +10400,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>703702</t>
+          <t>780820</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>463286</t>
+          <t>728729</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>803906</t>
+          <t>829649</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10435,32 +10435,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>654165</t>
+          <t>738834</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>478416</t>
+          <t>697117</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>744725</t>
+          <t>777817</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10470,32 +10470,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1357867</t>
+          <t>1519654</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1061264</t>
+          <t>1458004</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1505451</t>
+          <t>1589881</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>36,17%</t>
         </is>
       </c>
     </row>
@@ -10513,32 +10513,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>174674</t>
+          <t>193819</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>118859</t>
+          <t>165977</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>212320</t>
+          <t>225622</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10548,32 +10548,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>157091</t>
+          <t>180468</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>115417</t>
+          <t>161816</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>187045</t>
+          <t>207050</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10583,32 +10583,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>331765</t>
+          <t>374287</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>263446</t>
+          <t>338498</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>380564</t>
+          <t>413679</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -10626,32 +10626,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>48402</t>
+          <t>60630</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31016</t>
+          <t>46648</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62634</t>
+          <t>77221</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10661,32 +10661,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>264184</t>
+          <t>69203</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59131</t>
+          <t>55937</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>794574</t>
+          <t>85088</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10696,32 +10696,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>312586</t>
+          <t>129833</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>104674</t>
+          <t>110660</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>931266</t>
+          <t>157752</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -10739,32 +10739,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>19297</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9269</t>
+          <t>11720</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24676</t>
+          <t>29336</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10774,32 +10774,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>16371</t>
+          <t>21795</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9464</t>
+          <t>14118</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28623</t>
+          <t>37509</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10809,32 +10809,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>31848</t>
+          <t>41093</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>22569</t>
+          <t>30241</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>47546</t>
+          <t>55920</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -10852,17 +10852,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10887,17 +10887,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2231415</t>
+          <t>2164421</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2231415</t>
+          <t>2164421</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2231415</t>
+          <t>2164421</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10922,17 +10922,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4521742</t>
+          <t>4394987</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4521742</t>
+          <t>4394987</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4521742</t>
+          <t>4394987</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10969,32 +10969,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>391250</t>
+          <t>438014</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>359681</t>
+          <t>409401</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>417355</t>
+          <t>464727</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11004,32 +11004,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>449503</t>
+          <t>494415</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>426946</t>
+          <t>472197</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>467841</t>
+          <t>517407</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11039,32 +11039,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>840753</t>
+          <t>932429</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>806185</t>
+          <t>897592</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>872809</t>
+          <t>967867</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>67,13%</t>
         </is>
       </c>
     </row>
@@ -11082,32 +11082,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>190280</t>
+          <t>208768</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>166203</t>
+          <t>184426</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>218117</t>
+          <t>235745</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11117,32 +11117,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>165131</t>
+          <t>190580</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>148646</t>
+          <t>170647</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>183106</t>
+          <t>212009</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11152,32 +11152,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>355411</t>
+          <t>399349</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>328628</t>
+          <t>366154</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>385734</t>
+          <t>431053</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,9%</t>
         </is>
       </c>
     </row>
@@ -11195,27 +11195,27 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>35059</t>
+          <t>39117</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24705</t>
+          <t>28122</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49400</t>
+          <t>54374</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -11230,32 +11230,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>33724</t>
+          <t>36685</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24324</t>
+          <t>27226</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45584</t>
+          <t>49579</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11265,32 +11265,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>68783</t>
+          <t>75803</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>54373</t>
+          <t>61695</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>85166</t>
+          <t>94225</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -11308,32 +11308,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>15942</t>
+          <t>17686</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9131</t>
+          <t>10744</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30292</t>
+          <t>29437</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11343,32 +11343,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7605</t>
+          <t>8467</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4135</t>
+          <t>4727</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13415</t>
+          <t>14132</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11378,17 +11378,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>23547</t>
+          <t>26153</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15515</t>
+          <t>17726</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36221</t>
+          <t>39980</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -11421,22 +11421,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>11641</t>
+          <t>5509</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1509</t>
+          <t>1636</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>52658</t>
+          <t>13233</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -11446,7 +11446,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11456,22 +11456,22 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2469</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>705</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6912</t>
+          <t>6067</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -11481,7 +11481,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11491,32 +11491,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>14110</t>
+          <t>8151</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3779</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>52541</t>
+          <t>15515</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
           <t>1,08%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -11534,17 +11534,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>644172</t>
+          <t>709094</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>644172</t>
+          <t>709094</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>644172</t>
+          <t>709094</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11569,17 +11569,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>658432</t>
+          <t>732790</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>658432</t>
+          <t>732790</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>658432</t>
+          <t>732790</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11604,17 +11604,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1302604</t>
+          <t>1441884</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1302604</t>
+          <t>1441884</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1302604</t>
+          <t>1441884</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11651,32 +11651,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1974676</t>
+          <t>1876848</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1836656</t>
+          <t>1811043</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2291690</t>
+          <t>1943921</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11686,32 +11686,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1915401</t>
+          <t>1994037</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1534584</t>
+          <t>1939044</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2058275</t>
+          <t>2050537</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11721,32 +11721,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3890076</t>
+          <t>3870884</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3569820</t>
+          <t>3787383</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4202429</t>
+          <t>3958152</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>54,79%</t>
         </is>
       </c>
     </row>
@@ -11764,32 +11764,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1044137</t>
+          <t>1154569</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>819248</t>
+          <t>1091906</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1143854</t>
+          <t>1216099</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11799,32 +11799,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1047946</t>
+          <t>1184179</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>852099</t>
+          <t>1133368</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1134702</t>
+          <t>1234904</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11834,32 +11834,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2092083</t>
+          <t>2338748</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1824848</t>
+          <t>2257925</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2241758</t>
+          <t>2412893</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>33,4%</t>
         </is>
       </c>
     </row>
@@ -11877,32 +11877,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282878</t>
+          <t>320816</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>220472</t>
+          <t>286617</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>325757</t>
+          <t>359410</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11912,32 +11912,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>312006</t>
+          <t>350038</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>249322</t>
+          <t>321770</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>346208</t>
+          <t>381353</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11947,32 +11947,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>594884</t>
+          <t>670854</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>518245</t>
+          <t>627098</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>656576</t>
+          <t>718388</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -11990,32 +11990,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>105007</t>
+          <t>124770</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>79222</t>
+          <t>103821</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>128038</t>
+          <t>147636</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12025,32 +12025,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>323900</t>
+          <t>135637</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>119823</t>
+          <t>116614</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>952505</t>
+          <t>153337</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12060,32 +12060,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>428907</t>
+          <t>260406</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>220607</t>
+          <t>229204</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1127019</t>
+          <t>288890</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -12103,32 +12103,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>39301</t>
+          <t>37667</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>24934</t>
+          <t>26440</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>77336</t>
+          <t>51827</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12138,32 +12138,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>37503</t>
+          <t>46178</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>27332</t>
+          <t>35643</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>51187</t>
+          <t>61361</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12173,32 +12173,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>76804</t>
+          <t>83845</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>59418</t>
+          <t>68499</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>109949</t>
+          <t>103324</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -12216,17 +12216,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3445999</t>
+          <t>3514669</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3445999</t>
+          <t>3514669</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3445999</t>
+          <t>3514669</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12251,17 +12251,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3636756</t>
+          <t>3710069</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3636756</t>
+          <t>3710069</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3636756</t>
+          <t>3710069</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12286,17 +12286,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7082755</t>
+          <t>7224737</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7082755</t>
+          <t>7224737</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7082755</t>
+          <t>7224737</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
